--- a/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2884</v>
+        <v>0.3026</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3744</v>
+        <v>0.3754</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fault Tolerance</t>
+          <t>12e. Fault Tolerance</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.8568</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>14a. Maintainability</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.6465</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="6">
@@ -654,7 +654,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify that only the company user can access their products, routes, and profile.</t>
+          <t>Verify that only the company user can access their products/routes/profile.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -677,17 +677,137 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_R28c</t>
+          <t>CF_M08_R28a</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The profile of a company can only be edited and accessible by that
+          <t>The products of a company
+they can only be edited and accessible by that
 company.</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.449</v>
+        <v>0.4148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R_27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The system shall use Blockchain technology to ensure transparency and traceability.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CF_M08_R16a</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The system should support Spanish (verified by a translator).</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R_28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The system architecture shall be based on microservices.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CF_M08_R24b</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>The system must be compatible with the
+most common mobile devices.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1475</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R_29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The system shall use Amazon EC2 instances managed by Docker.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CF_M08_R06</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>The system must be able to save all the images of all the products and users of the
+system.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1117</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3026</v>
+        <v>0.3029</v>
       </c>
     </row>
     <row r="3">
@@ -548,18 +548,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3754</v>
+        <v>0.3756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime and be able to recover from failures in less than 1 hour.</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,28 +586,27 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_R21a</t>
+          <t>CF_M08_R21b</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The system must be able to recover from failures
-in less than 1 hour.</t>
+          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.856</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_19b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The system must be easy to maintain and update with clear and complete documentation.</t>
+          <t>The system must have clear and complete documentation.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -643,7 +642,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.6478</v>
+        <v>0.6456</v>
       </c>
     </row>
     <row r="6">
@@ -688,7 +687,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.4148</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="7">
@@ -727,7 +726,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.101</v>
+        <v>0.1009</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +766,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.1475</v>
+        <v>0.1471</v>
       </c>
     </row>
     <row r="9">
@@ -807,7 +806,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.1117</v>
+        <v>0.1113</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_01a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The system shall be available in both Spanish and English.</t>
+          <t>The system shall be available in Spanish.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,7 +497,11 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>CF_M08_R15</t>
@@ -509,18 +513,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3029</v>
+        <v>0.3546</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_01b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
+          <t>The system shall be available in English.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -536,208 +540,218 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M08_R29</t>
+          <t>CF_M08_R15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
+          <t>The system must be available in different languages</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3756</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_17a</t>
+          <t>R_08b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime.</t>
+          <t>A company shall have access to a dashboard to view additional information.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12e. Fault Tolerance</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M08_R21b</t>
+          <t>CF_M08_R08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
+          <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.654</v>
+        <v>0.5712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_19b</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The system must have clear and complete documentation.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>14a. Maintainability</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M08_R22b</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Complete and updated documentation</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.6456</v>
+        <v>0.3764</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify that only the company user can access their products/routes/profile.</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12e. Fault Tolerance</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M08_R28a</t>
+          <t>CF_M08_R21b</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.417</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_19b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The system shall use Blockchain technology to ensure transparency and traceability.</t>
+          <t>The system must have clear and complete documentation.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>14a. Maintainability</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M08_R16a</t>
+          <t>CF_M08_R22b</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The system should support Spanish (verified by a translator).</t>
+          <t>Complete and updated documentation</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.1009</v>
+        <v>0.6655</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The system architecture shall be based on microservices.</t>
+          <t>The system shall use Blockchain technology to ensure transparency and traceability.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -747,7 +761,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -756,28 +770,27 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R16a</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common mobile devices.</t>
+          <t>The system should support Spanish (verified by a translator).</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.1471</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_29</t>
+          <t>R_28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The system shall use Amazon EC2 instances managed by Docker.</t>
+          <t>The system architecture shall be based on microservices.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -796,17 +809,55 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
+          <t>CF_M08_R24b</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>The system must be compatible with the most common mobile devices.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R_29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The system shall use Amazon EC2 instances managed by Docker.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>CF_M08_R06</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>The system must be able to save all the images of all the products and users of the
-system.</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1113</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>The system must be able to save all the images of all the products and users of the system.</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1074</v>
       </c>
     </row>
   </sheetData>
